--- a/data-manipulation-scripts/sheets-cleanup/sheets/BUCHA BALANCA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BUCHA BALANCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -75,6 +75,9 @@
   <si>
     <t>JOGO BUCHA BALANCA XTZ125 150/ CROSSER</t>
   </si>
+  <si>
+    <t xml:space="preserve">JOGO BUCHA BALANÇA HONDA TITAN </t>
+  </si>
 </sst>
 </file>
 
@@ -134,7 +137,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -407,7 +410,9 @@
       <c r="C2" s="4">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -441,7 +446,9 @@
       <c r="C3" s="4">
         <v>1.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -511,7 +518,9 @@
       <c r="C5" s="7">
         <v>3.0</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -545,7 +554,9 @@
       <c r="C6" s="7">
         <v>1.0</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -579,7 +590,9 @@
       <c r="C7" s="7">
         <v>1.0</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -677,9 +690,15 @@
     </row>
     <row r="10">
       <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>40.0</v>
+      </c>
       <c r="E10" s="9"/>
     </row>
     <row r="11">
